--- a/data.mn/public/datasets/bop-trade-balance.xlsx
+++ b/data.mn/public/datasets/bop-trade-balance.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,17 +431,17 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>exports</t>
+          <t>Exports</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>imports</t>
+          <t>Imports</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>net</t>
+          <t>Net Balance</t>
         </is>
       </c>
     </row>
@@ -553,7 +554,7 @@
         <v>188.064</v>
       </c>
       <c r="D8" t="n">
-        <v>-29.12799999999999</v>
+        <v>-29.12799999999998</v>
       </c>
     </row>
     <row r="9">
@@ -729,7 +730,7 @@
         <v>295.665</v>
       </c>
       <c r="D19" t="n">
-        <v>23.08199999999999</v>
+        <v>23.082</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1658,7 @@
         <v>338.862</v>
       </c>
       <c r="D77" t="n">
-        <v>37.31199999999995</v>
+        <v>37.31199999999996</v>
       </c>
     </row>
     <row r="78">
@@ -2041,7 +2042,7 @@
         <v>343.112</v>
       </c>
       <c r="D101" t="n">
-        <v>194.7549999999999</v>
+        <v>194.755</v>
       </c>
     </row>
     <row r="102">
@@ -2201,7 +2202,7 @@
         <v>361.494</v>
       </c>
       <c r="D111" t="n">
-        <v>-30.64600000000002</v>
+        <v>-30.64600000000001</v>
       </c>
     </row>
     <row r="112">
@@ -2345,7 +2346,7 @@
         <v>496.948</v>
       </c>
       <c r="D120" t="n">
-        <v>31.87700000000007</v>
+        <v>31.87700000000006</v>
       </c>
     </row>
     <row r="121">
@@ -2457,7 +2458,7 @@
         <v>559.396</v>
       </c>
       <c r="D127" t="n">
-        <v>97.54600000000005</v>
+        <v>97.54600000000003</v>
       </c>
     </row>
     <row r="128">
@@ -2473,7 +2474,7 @@
         <v>609.109</v>
       </c>
       <c r="D128" t="n">
-        <v>-26.68299999999999</v>
+        <v>-26.683</v>
       </c>
     </row>
     <row r="129">
@@ -2569,7 +2570,7 @@
         <v>475.284</v>
       </c>
       <c r="D134" t="n">
-        <v>-99.15899999999999</v>
+        <v>-99.15900000000001</v>
       </c>
     </row>
     <row r="135">
@@ -2665,7 +2666,7 @@
         <v>474.357</v>
       </c>
       <c r="D140" t="n">
-        <v>447.5049999999999</v>
+        <v>447.505</v>
       </c>
     </row>
     <row r="141">
@@ -2777,7 +2778,7 @@
         <v>452.352</v>
       </c>
       <c r="D147" t="n">
-        <v>94.29700000000003</v>
+        <v>94.29700000000004</v>
       </c>
     </row>
     <row r="148">
@@ -2793,7 +2794,7 @@
         <v>583.146</v>
       </c>
       <c r="D148" t="n">
-        <v>100.2670000000001</v>
+        <v>100.267</v>
       </c>
     </row>
     <row r="149">
@@ -3305,7 +3306,7 @@
         <v>842.9349999999999</v>
       </c>
       <c r="D180" t="n">
-        <v>428.671</v>
+        <v>428.6710000000001</v>
       </c>
     </row>
     <row r="181">
@@ -3337,7 +3338,7 @@
         <v>946.3099999999999</v>
       </c>
       <c r="D182" t="n">
-        <v>221.047</v>
+        <v>221.0470000000001</v>
       </c>
     </row>
     <row r="183">
@@ -3705,7 +3706,7 @@
         <v>1158.19</v>
       </c>
       <c r="D205" t="n">
-        <v>907.0999999999999</v>
+        <v>907.1</v>
       </c>
     </row>
     <row r="206">
@@ -3801,7 +3802,3409 @@
         <v>1175.867</v>
       </c>
       <c r="D211" t="n">
-        <v>918.4860000000001</v>
+        <v>918.486</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D211"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Импорт</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Цэвэр тэнцэл</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Экспорт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2009-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>120.737</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="D2" t="n">
+        <v>170.077</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2009-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>73.39</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-12.023</v>
+      </c>
+      <c r="D3" t="n">
+        <v>61.367</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2009-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>177.608</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-87.92100000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>89.687</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2009-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>138.543</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-16.93100000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>121.612</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2009-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>152.303</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-3.925000000000011</v>
+      </c>
+      <c r="D6" t="n">
+        <v>148.378</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2009-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>193.242</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-23.58699999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>169.655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2009-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>188.064</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-29.12799999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>158.936</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>178.793</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-19.124</v>
+      </c>
+      <c r="D9" t="n">
+        <v>159.669</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>207.447</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-24.03800000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>183.409</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>213.295</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-20.38299999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>192.912</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>199.94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-8.967999999999989</v>
+      </c>
+      <c r="D12" t="n">
+        <v>190.972</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>215.701</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18.49200000000002</v>
+      </c>
+      <c r="D13" t="n">
+        <v>234.193</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2010-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>126.362</v>
+      </c>
+      <c r="C14" t="n">
+        <v>36.92699999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>163.289</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2010-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>158.84</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-10.732</v>
+      </c>
+      <c r="D15" t="n">
+        <v>148.108</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2010-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>271.049</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-83.81499999999997</v>
+      </c>
+      <c r="D16" t="n">
+        <v>187.234</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2010-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>237.626</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-7.271000000000015</v>
+      </c>
+      <c r="D17" t="n">
+        <v>230.355</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2010-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>219.062</v>
+      </c>
+      <c r="C18" t="n">
+        <v>41.40199999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>260.464</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>295.665</v>
+      </c>
+      <c r="C19" t="n">
+        <v>23.082</v>
+      </c>
+      <c r="D19" t="n">
+        <v>318.747</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>302.325</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-72.58399999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>229.741</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2010-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>285.441</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-30.34699999999998</v>
+      </c>
+      <c r="D21" t="n">
+        <v>255.094</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2010-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>272.98</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-40.94500000000002</v>
+      </c>
+      <c r="D22" t="n">
+        <v>232.035</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2010-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>271.298</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-21.01599999999999</v>
+      </c>
+      <c r="D23" t="n">
+        <v>250.282</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2010-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>324.677</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-49.98500000000001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>274.692</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2010-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>314.568</v>
+      </c>
+      <c r="C25" t="n">
+        <v>43.27100000000002</v>
+      </c>
+      <c r="D25" t="n">
+        <v>357.839</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2011-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>369.549</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-171.043</v>
+      </c>
+      <c r="D26" t="n">
+        <v>198.506</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2011-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>267.375</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-73.64400000000001</v>
+      </c>
+      <c r="D27" t="n">
+        <v>193.731</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2011-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>481.012</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-173.252</v>
+      </c>
+      <c r="D28" t="n">
+        <v>307.76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2011-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>511.574</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-160.62</v>
+      </c>
+      <c r="D29" t="n">
+        <v>350.954</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2011-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>547.963</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-213.013</v>
+      </c>
+      <c r="D30" t="n">
+        <v>334.95</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>620.356</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-269.171</v>
+      </c>
+      <c r="D31" t="n">
+        <v>351.185</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2011-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>721.49</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-429.488</v>
+      </c>
+      <c r="D32" t="n">
+        <v>292.002</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>762.429</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-328.609</v>
+      </c>
+      <c r="D33" t="n">
+        <v>433.82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2011-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>667.53</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-277.361</v>
+      </c>
+      <c r="D34" t="n">
+        <v>390.169</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2011-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>542.995</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-172.653</v>
+      </c>
+      <c r="D35" t="n">
+        <v>370.342</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2011-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>618.792</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-222.749</v>
+      </c>
+      <c r="D36" t="n">
+        <v>396.043</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2011-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>614.088</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-177.552</v>
+      </c>
+      <c r="D37" t="n">
+        <v>436.536</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2012-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>496.504</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-299.776</v>
+      </c>
+      <c r="D38" t="n">
+        <v>196.728</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2012-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>479.469</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-234.711</v>
+      </c>
+      <c r="D39" t="n">
+        <v>244.758</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>546.213</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-245.316</v>
+      </c>
+      <c r="D40" t="n">
+        <v>300.897</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2012-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>597.605</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-263.727</v>
+      </c>
+      <c r="D41" t="n">
+        <v>333.878</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2012-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>664.23</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-335.415</v>
+      </c>
+      <c r="D42" t="n">
+        <v>328.815</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2012-06</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>594.365</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-120.582</v>
+      </c>
+      <c r="D43" t="n">
+        <v>473.783</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>663.771</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-425.351</v>
+      </c>
+      <c r="D44" t="n">
+        <v>238.42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>698.318</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-406.755</v>
+      </c>
+      <c r="D45" t="n">
+        <v>291.563</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>574.188</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-239.374</v>
+      </c>
+      <c r="D46" t="n">
+        <v>334.814</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2012-10</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>504.926</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-111.932</v>
+      </c>
+      <c r="D47" t="n">
+        <v>392.994</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>536.275</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-192.646</v>
+      </c>
+      <c r="D48" t="n">
+        <v>343.629</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2012-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>474.393</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-154.2209999999999</v>
+      </c>
+      <c r="D49" t="n">
+        <v>320.172</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2013-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>507.204</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-246.967</v>
+      </c>
+      <c r="D50" t="n">
+        <v>260.237</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2013-02</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>310.73</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-119.149</v>
+      </c>
+      <c r="D51" t="n">
+        <v>191.581</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2013-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>401.652</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-128.71</v>
+      </c>
+      <c r="D52" t="n">
+        <v>272.942</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2013-04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>537.155</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-208.756</v>
+      </c>
+      <c r="D53" t="n">
+        <v>328.399</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2013-05</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>735.295</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-355.3489999999999</v>
+      </c>
+      <c r="D54" t="n">
+        <v>379.946</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>593.853</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-275.5069999999999</v>
+      </c>
+      <c r="D55" t="n">
+        <v>318.346</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>618.313</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-310.01</v>
+      </c>
+      <c r="D56" t="n">
+        <v>308.303</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2013-08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>587.378</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-283.595</v>
+      </c>
+      <c r="D57" t="n">
+        <v>303.783</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>571.897</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-233.821</v>
+      </c>
+      <c r="D58" t="n">
+        <v>338.076</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2013-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>539.888</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-181.7090000000001</v>
+      </c>
+      <c r="D59" t="n">
+        <v>358.179</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2013-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>494.557</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-141.256</v>
+      </c>
+      <c r="D60" t="n">
+        <v>353.301</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2013-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>499.55</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-123.274</v>
+      </c>
+      <c r="D61" t="n">
+        <v>376.276</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>339.122</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-46.584</v>
+      </c>
+      <c r="D62" t="n">
+        <v>292.538</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2014-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>280.361</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-25.136</v>
+      </c>
+      <c r="D63" t="n">
+        <v>255.225</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2014-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>388.436</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-26.33699999999999</v>
+      </c>
+      <c r="D64" t="n">
+        <v>362.099</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2014-04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>530.2569999999999</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-106.4309999999999</v>
+      </c>
+      <c r="D65" t="n">
+        <v>423.826</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2014-05</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>571.364</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-98.56000000000006</v>
+      </c>
+      <c r="D66" t="n">
+        <v>472.804</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2014-06</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>505.679</v>
+      </c>
+      <c r="C67" t="n">
+        <v>11.86900000000003</v>
+      </c>
+      <c r="D67" t="n">
+        <v>517.548</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>528.141</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-83.99799999999999</v>
+      </c>
+      <c r="D68" t="n">
+        <v>444.143</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2014-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>467.141</v>
+      </c>
+      <c r="C69" t="n">
+        <v>140.565</v>
+      </c>
+      <c r="D69" t="n">
+        <v>607.706</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>477.595</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-46.18100000000004</v>
+      </c>
+      <c r="D70" t="n">
+        <v>431.414</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2014-10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>433.682</v>
+      </c>
+      <c r="C71" t="n">
+        <v>120.792</v>
+      </c>
+      <c r="D71" t="n">
+        <v>554.474</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2014-11</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>371.117</v>
+      </c>
+      <c r="C72" t="n">
+        <v>185.036</v>
+      </c>
+      <c r="D72" t="n">
+        <v>556.153</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2014-12</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>400.24</v>
+      </c>
+      <c r="C73" t="n">
+        <v>152.678</v>
+      </c>
+      <c r="D73" t="n">
+        <v>552.918</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2015-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>255.374</v>
+      </c>
+      <c r="C74" t="n">
+        <v>129.162</v>
+      </c>
+      <c r="D74" t="n">
+        <v>384.536</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2015-02</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>220.99</v>
+      </c>
+      <c r="C75" t="n">
+        <v>139.472</v>
+      </c>
+      <c r="D75" t="n">
+        <v>360.462</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2015-03</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>243.859</v>
+      </c>
+      <c r="C76" t="n">
+        <v>115.609</v>
+      </c>
+      <c r="D76" t="n">
+        <v>359.468</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2015-04</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>338.862</v>
+      </c>
+      <c r="C77" t="n">
+        <v>37.31199999999996</v>
+      </c>
+      <c r="D77" t="n">
+        <v>376.174</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2015-05</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>416.624</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-93.767</v>
+      </c>
+      <c r="D78" t="n">
+        <v>322.857</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2015-06</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="C79" t="n">
+        <v>71.52299999999997</v>
+      </c>
+      <c r="D79" t="n">
+        <v>470.263</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2015-07</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>372.901</v>
+      </c>
+      <c r="C80" t="n">
+        <v>21.88900000000001</v>
+      </c>
+      <c r="D80" t="n">
+        <v>394.79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2015-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>349.815</v>
+      </c>
+      <c r="C81" t="n">
+        <v>83.084</v>
+      </c>
+      <c r="D81" t="n">
+        <v>432.899</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2015-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>323.867</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-7.194999999999993</v>
+      </c>
+      <c r="D82" t="n">
+        <v>316.672</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2015-10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>314.659</v>
+      </c>
+      <c r="C83" t="n">
+        <v>24.923</v>
+      </c>
+      <c r="D83" t="n">
+        <v>339.582</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2015-11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>338.831</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-78.84800000000001</v>
+      </c>
+      <c r="D84" t="n">
+        <v>259.983</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2015-12</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>309.276</v>
+      </c>
+      <c r="C85" t="n">
+        <v>119.44</v>
+      </c>
+      <c r="D85" t="n">
+        <v>428.716</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>211.003</v>
+      </c>
+      <c r="C86" t="n">
+        <v>87.42700000000002</v>
+      </c>
+      <c r="D86" t="n">
+        <v>298.43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>156.652</v>
+      </c>
+      <c r="C87" t="n">
+        <v>152.002</v>
+      </c>
+      <c r="D87" t="n">
+        <v>308.654</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>251.259</v>
+      </c>
+      <c r="C88" t="n">
+        <v>134.009</v>
+      </c>
+      <c r="D88" t="n">
+        <v>385.268</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>275.613</v>
+      </c>
+      <c r="C89" t="n">
+        <v>109.149</v>
+      </c>
+      <c r="D89" t="n">
+        <v>384.762</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>316.216</v>
+      </c>
+      <c r="C90" t="n">
+        <v>54.15800000000002</v>
+      </c>
+      <c r="D90" t="n">
+        <v>370.374</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>341.786</v>
+      </c>
+      <c r="C91" t="n">
+        <v>85.01499999999999</v>
+      </c>
+      <c r="D91" t="n">
+        <v>426.801</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-6.543000000000006</v>
+      </c>
+      <c r="D92" t="n">
+        <v>332.767</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>357.993</v>
+      </c>
+      <c r="C93" t="n">
+        <v>53.279</v>
+      </c>
+      <c r="D93" t="n">
+        <v>411.272</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>285.019</v>
+      </c>
+      <c r="C94" t="n">
+        <v>63.46600000000001</v>
+      </c>
+      <c r="D94" t="n">
+        <v>348.485</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>327.022</v>
+      </c>
+      <c r="C95" t="n">
+        <v>22.53700000000003</v>
+      </c>
+      <c r="D95" t="n">
+        <v>349.559</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>318.009</v>
+      </c>
+      <c r="C96" t="n">
+        <v>232.28</v>
+      </c>
+      <c r="D96" t="n">
+        <v>550.289</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>286.312</v>
+      </c>
+      <c r="C97" t="n">
+        <v>351.005</v>
+      </c>
+      <c r="D97" t="n">
+        <v>637.317</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>285.239</v>
+      </c>
+      <c r="C98" t="n">
+        <v>109.364</v>
+      </c>
+      <c r="D98" t="n">
+        <v>394.603</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>219.181</v>
+      </c>
+      <c r="C99" t="n">
+        <v>178.73</v>
+      </c>
+      <c r="D99" t="n">
+        <v>397.911</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>280.01</v>
+      </c>
+      <c r="C100" t="n">
+        <v>137.239</v>
+      </c>
+      <c r="D100" t="n">
+        <v>417.249</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>343.112</v>
+      </c>
+      <c r="C101" t="n">
+        <v>194.755</v>
+      </c>
+      <c r="D101" t="n">
+        <v>537.867</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>380.539</v>
+      </c>
+      <c r="C102" t="n">
+        <v>224.2140000000001</v>
+      </c>
+      <c r="D102" t="n">
+        <v>604.753</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>428.314</v>
+      </c>
+      <c r="C103" t="n">
+        <v>111.6159999999999</v>
+      </c>
+      <c r="D103" t="n">
+        <v>539.9299999999999</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>405.047</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-29.01500000000004</v>
+      </c>
+      <c r="D104" t="n">
+        <v>376.032</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>422.555</v>
+      </c>
+      <c r="C105" t="n">
+        <v>161.397</v>
+      </c>
+      <c r="D105" t="n">
+        <v>583.952</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>376.937</v>
+      </c>
+      <c r="C106" t="n">
+        <v>83.87200000000001</v>
+      </c>
+      <c r="D106" t="n">
+        <v>460.809</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>398.605</v>
+      </c>
+      <c r="C107" t="n">
+        <v>177.533</v>
+      </c>
+      <c r="D107" t="n">
+        <v>576.138</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>374.245</v>
+      </c>
+      <c r="C108" t="n">
+        <v>76.24399999999997</v>
+      </c>
+      <c r="D108" t="n">
+        <v>450.489</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>426.853</v>
+      </c>
+      <c r="C109" t="n">
+        <v>67.72300000000001</v>
+      </c>
+      <c r="D109" t="n">
+        <v>494.576</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>364.802</v>
+      </c>
+      <c r="C110" t="n">
+        <v>61.13499999999999</v>
+      </c>
+      <c r="D110" t="n">
+        <v>425.937</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>361.494</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-30.64600000000001</v>
+      </c>
+      <c r="D111" t="n">
+        <v>330.848</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>406.191</v>
+      </c>
+      <c r="C112" t="n">
+        <v>208.059</v>
+      </c>
+      <c r="D112" t="n">
+        <v>614.25</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>448.597</v>
+      </c>
+      <c r="C113" t="n">
+        <v>173.9640000000001</v>
+      </c>
+      <c r="D113" t="n">
+        <v>622.561</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>599.581</v>
+      </c>
+      <c r="C114" t="n">
+        <v>94.99199999999996</v>
+      </c>
+      <c r="D114" t="n">
+        <v>694.573</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>577.879</v>
+      </c>
+      <c r="C115" t="n">
+        <v>86.48699999999997</v>
+      </c>
+      <c r="D115" t="n">
+        <v>664.366</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>503.608</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-5.334000000000003</v>
+      </c>
+      <c r="D116" t="n">
+        <v>498.274</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>545.169</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-48.56700000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>496.602</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>548.7089999999999</v>
+      </c>
+      <c r="C118" t="n">
+        <v>38.1110000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>586.8200000000001</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>524.649</v>
+      </c>
+      <c r="C119" t="n">
+        <v>47.23199999999997</v>
+      </c>
+      <c r="D119" t="n">
+        <v>571.881</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>496.948</v>
+      </c>
+      <c r="C120" t="n">
+        <v>31.87700000000006</v>
+      </c>
+      <c r="D120" t="n">
+        <v>528.825</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>503.406</v>
+      </c>
+      <c r="C121" t="n">
+        <v>18.20099999999996</v>
+      </c>
+      <c r="D121" t="n">
+        <v>521.607</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>473.404</v>
+      </c>
+      <c r="C122" t="n">
+        <v>148.997</v>
+      </c>
+      <c r="D122" t="n">
+        <v>622.401</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>309.308</v>
+      </c>
+      <c r="C123" t="n">
+        <v>130.699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>440.007</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>449.666</v>
+      </c>
+      <c r="C124" t="n">
+        <v>184.485</v>
+      </c>
+      <c r="D124" t="n">
+        <v>634.151</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>481.67</v>
+      </c>
+      <c r="C125" t="n">
+        <v>225.104</v>
+      </c>
+      <c r="D125" t="n">
+        <v>706.774</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>521.3869999999999</v>
+      </c>
+      <c r="C126" t="n">
+        <v>168.2180000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>689.605</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>559.396</v>
+      </c>
+      <c r="C127" t="n">
+        <v>97.54600000000003</v>
+      </c>
+      <c r="D127" t="n">
+        <v>656.942</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>609.109</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-26.683</v>
+      </c>
+      <c r="D128" t="n">
+        <v>582.426</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>587.351</v>
+      </c>
+      <c r="C129" t="n">
+        <v>180.352</v>
+      </c>
+      <c r="D129" t="n">
+        <v>767.703</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>507.049</v>
+      </c>
+      <c r="C130" t="n">
+        <v>21.70500000000004</v>
+      </c>
+      <c r="D130" t="n">
+        <v>528.754</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>465.425</v>
+      </c>
+      <c r="C131" t="n">
+        <v>49.65100000000001</v>
+      </c>
+      <c r="D131" t="n">
+        <v>515.076</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>519.4109999999999</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-22.14299999999997</v>
+      </c>
+      <c r="D132" t="n">
+        <v>497.268</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>541.557</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.18100000000004</v>
+      </c>
+      <c r="D133" t="n">
+        <v>541.7380000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>475.284</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-99.15900000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>376.125</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>272.504</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-12.62100000000004</v>
+      </c>
+      <c r="D135" t="n">
+        <v>259.883</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>403.049</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-185.039</v>
+      </c>
+      <c r="D136" t="n">
+        <v>218.01</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>417.266</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-123.433</v>
+      </c>
+      <c r="D137" t="n">
+        <v>293.833</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>400.373</v>
+      </c>
+      <c r="C138" t="n">
+        <v>210.864</v>
+      </c>
+      <c r="D138" t="n">
+        <v>611.237</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>460.11</v>
+      </c>
+      <c r="C139" t="n">
+        <v>354.465</v>
+      </c>
+      <c r="D139" t="n">
+        <v>814.575</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>474.357</v>
+      </c>
+      <c r="C140" t="n">
+        <v>447.505</v>
+      </c>
+      <c r="D140" t="n">
+        <v>921.862</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>506.05</v>
+      </c>
+      <c r="C141" t="n">
+        <v>157.892</v>
+      </c>
+      <c r="D141" t="n">
+        <v>663.942</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>469.099</v>
+      </c>
+      <c r="C142" t="n">
+        <v>117.333</v>
+      </c>
+      <c r="D142" t="n">
+        <v>586.432</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>501.729</v>
+      </c>
+      <c r="C143" t="n">
+        <v>237.6390000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>739.3680000000001</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>447.222</v>
+      </c>
+      <c r="C144" t="n">
+        <v>393.8670000000001</v>
+      </c>
+      <c r="D144" t="n">
+        <v>841.0890000000001</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>408.061</v>
+      </c>
+      <c r="C145" t="n">
+        <v>256.246</v>
+      </c>
+      <c r="D145" t="n">
+        <v>664.307</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>444.241</v>
+      </c>
+      <c r="C146" t="n">
+        <v>154.133</v>
+      </c>
+      <c r="D146" t="n">
+        <v>598.374</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>452.352</v>
+      </c>
+      <c r="C147" t="n">
+        <v>94.29700000000004</v>
+      </c>
+      <c r="D147" t="n">
+        <v>546.649</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>583.146</v>
+      </c>
+      <c r="C148" t="n">
+        <v>100.267</v>
+      </c>
+      <c r="D148" t="n">
+        <v>683.413</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>436.562</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-72.572</v>
+      </c>
+      <c r="D149" t="n">
+        <v>363.99</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>636.973</v>
+      </c>
+      <c r="C150" t="n">
+        <v>38.83699999999999</v>
+      </c>
+      <c r="D150" t="n">
+        <v>675.8099999999999</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>655.33</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-20.31200000000001</v>
+      </c>
+      <c r="D151" t="n">
+        <v>635.018</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>563.456</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-38.91100000000006</v>
+      </c>
+      <c r="D152" t="n">
+        <v>524.545</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>623.99</v>
+      </c>
+      <c r="C153" t="n">
+        <v>124.766</v>
+      </c>
+      <c r="D153" t="n">
+        <v>748.756</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>649.09</v>
+      </c>
+      <c r="C154" t="n">
+        <v>61.90999999999997</v>
+      </c>
+      <c r="D154" t="n">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>516.902</v>
+      </c>
+      <c r="C155" t="n">
+        <v>522.1859999999999</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1039.088</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>544.275</v>
+      </c>
+      <c r="C156" t="n">
+        <v>733.3750000000001</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1277.65</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>659.798</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-328.351</v>
+      </c>
+      <c r="D157" t="n">
+        <v>331.447</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>567.362</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-105.845</v>
+      </c>
+      <c r="D158" t="n">
+        <v>461.517</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>498.109</v>
+      </c>
+      <c r="C159" t="n">
+        <v>40.22600000000006</v>
+      </c>
+      <c r="D159" t="n">
+        <v>538.335</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>657.192</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-91.16499999999996</v>
+      </c>
+      <c r="D160" t="n">
+        <v>566.027</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>657.253</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-84.471</v>
+      </c>
+      <c r="D161" t="n">
+        <v>572.782</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>783.227</v>
+      </c>
+      <c r="C162" t="n">
+        <v>85.15100000000007</v>
+      </c>
+      <c r="D162" t="n">
+        <v>868.378</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>798.4589999999999</v>
+      </c>
+      <c r="C163" t="n">
+        <v>37.02100000000007</v>
+      </c>
+      <c r="D163" t="n">
+        <v>835.48</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>789.3440000000001</v>
+      </c>
+      <c r="C164" t="n">
+        <v>62.60399999999993</v>
+      </c>
+      <c r="D164" t="n">
+        <v>851.948</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>819.7190000000001</v>
+      </c>
+      <c r="C165" t="n">
+        <v>187.62</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1007.339</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>739.02</v>
+      </c>
+      <c r="C166" t="n">
+        <v>331.692</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1070.712</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>777.6130000000001</v>
+      </c>
+      <c r="C167" t="n">
+        <v>138.1859999999999</v>
+      </c>
+      <c r="D167" t="n">
+        <v>915.799</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>718.848</v>
+      </c>
+      <c r="C168" t="n">
+        <v>352.702</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1071.55</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>815.537</v>
+      </c>
+      <c r="C169" t="n">
+        <v>278.798</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1094.335</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>688.381</v>
+      </c>
+      <c r="C170" t="n">
+        <v>316.874</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1005.255</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>513.596</v>
+      </c>
+      <c r="C171" t="n">
+        <v>576.883</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1090.479</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>743.125</v>
+      </c>
+      <c r="C172" t="n">
+        <v>509.6469999999999</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1252.772</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>728.711</v>
+      </c>
+      <c r="C173" t="n">
+        <v>464.068</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1192.779</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>810.938</v>
+      </c>
+      <c r="C174" t="n">
+        <v>244.053</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1054.991</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>812.934</v>
+      </c>
+      <c r="C175" t="n">
+        <v>328.9870000000001</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1141.921</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>754.7619999999999</v>
+      </c>
+      <c r="C176" t="n">
+        <v>342.6079999999999</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1097.37</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>941.465</v>
+      </c>
+      <c r="C177" t="n">
+        <v>329.2420000000001</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1270.707</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>823.371</v>
+      </c>
+      <c r="C178" t="n">
+        <v>385.8480000000001</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1209.219</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>806.044</v>
+      </c>
+      <c r="C179" t="n">
+        <v>254.3750000000001</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1060.419</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>842.9349999999999</v>
+      </c>
+      <c r="C180" t="n">
+        <v>428.6710000000001</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1271.606</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>899.383</v>
+      </c>
+      <c r="C181" t="n">
+        <v>367.395</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1266.778</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>946.3099999999999</v>
+      </c>
+      <c r="C182" t="n">
+        <v>221.0470000000001</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1167.357</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>675.593</v>
+      </c>
+      <c r="C183" t="n">
+        <v>157.2700000000001</v>
+      </c>
+      <c r="D183" t="n">
+        <v>832.8630000000001</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>864.265</v>
+      </c>
+      <c r="C184" t="n">
+        <v>566.4820000000001</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1430.747</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1082.413</v>
+      </c>
+      <c r="C185" t="n">
+        <v>109.6659999999999</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1192.079</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>948.093</v>
+      </c>
+      <c r="C186" t="n">
+        <v>389.88</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1337.973</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>984.101</v>
+      </c>
+      <c r="C187" t="n">
+        <v>498.081</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1482.182</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1023.975</v>
+      </c>
+      <c r="C188" t="n">
+        <v>253.6909999999999</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1277.666</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1087.724</v>
+      </c>
+      <c r="C189" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1316.524</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1087.127</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-60.779</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1026.348</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>973.6900000000001</v>
+      </c>
+      <c r="C191" t="n">
+        <v>347.614</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1321.304</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>977.8440000000001</v>
+      </c>
+      <c r="C192" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1326.564</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1017.284</v>
+      </c>
+      <c r="C193" t="n">
+        <v>20.98300000000006</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1038.267</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>984.11</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-5.350000000000023</v>
+      </c>
+      <c r="D194" t="n">
+        <v>978.76</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>761.05</v>
+      </c>
+      <c r="C195" t="n">
+        <v>193.46</v>
+      </c>
+      <c r="D195" t="n">
+        <v>954.51</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>837.24</v>
+      </c>
+      <c r="C196" t="n">
+        <v>71.25999999999999</v>
+      </c>
+      <c r="D196" t="n">
+        <v>908.5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1012.37</v>
+      </c>
+      <c r="C197" t="n">
+        <v>146.2900000000001</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1158.66</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>962.38</v>
+      </c>
+      <c r="C198" t="n">
+        <v>137.5000000000001</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1099.88</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>962.75</v>
+      </c>
+      <c r="C199" t="n">
+        <v>177.53</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1140.28</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>958.5700000000001</v>
+      </c>
+      <c r="C200" t="n">
+        <v>103.91</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1062.48</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>960</v>
+      </c>
+      <c r="C201" t="n">
+        <v>407.1500000000001</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1367.15</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1048.44</v>
+      </c>
+      <c r="C202" t="n">
+        <v>567.0599999999999</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1615.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>866.77</v>
+      </c>
+      <c r="C203" t="n">
+        <v>632.55</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1499.32</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>821.46</v>
+      </c>
+      <c r="C204" t="n">
+        <v>673.97</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1495.43</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1158.19</v>
+      </c>
+      <c r="C205" t="n">
+        <v>907.1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>2065.29</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>835.932</v>
+      </c>
+      <c r="C206" t="n">
+        <v>841.3810000000001</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1677.313</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>711.818</v>
+      </c>
+      <c r="C207" t="n">
+        <v>719.509</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1431.327</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>883.929</v>
+      </c>
+      <c r="C208" t="n">
+        <v>945.2089999999999</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1829.138</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1162.754</v>
+      </c>
+      <c r="C209" t="n">
+        <v>827.77</v>
+      </c>
+      <c r="D209" t="n">
+        <v>1990.524</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1213.874</v>
+      </c>
+      <c r="C210" t="n">
+        <v>261.1120000000001</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1474.986</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>1175.867</v>
+      </c>
+      <c r="C211" t="n">
+        <v>918.486</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2094.353</v>
       </c>
     </row>
   </sheetData>

--- a/data.mn/public/datasets/bop-trade-balance.xlsx
+++ b/data.mn/public/datasets/bop-trade-balance.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3764,13 +3764,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1990.524</v>
+        <v>1986.894</v>
       </c>
       <c r="C209" t="n">
-        <v>1162.754</v>
+        <v>1166.092</v>
       </c>
       <c r="D209" t="n">
-        <v>827.77</v>
+        <v>820.8019999999999</v>
       </c>
     </row>
     <row r="210">
@@ -3780,13 +3780,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1474.986</v>
+        <v>1471.401</v>
       </c>
       <c r="C210" t="n">
-        <v>1213.874</v>
+        <v>1218.445</v>
       </c>
       <c r="D210" t="n">
-        <v>261.1120000000001</v>
+        <v>252.9560000000001</v>
       </c>
     </row>
     <row r="211">
@@ -3796,13 +3796,45 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>2094.353</v>
+        <v>2081.587</v>
       </c>
       <c r="C211" t="n">
-        <v>1175.867</v>
+        <v>1180.552</v>
       </c>
       <c r="D211" t="n">
-        <v>918.486</v>
+        <v>901.035</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1682.079</v>
+      </c>
+      <c r="C212" t="n">
+        <v>1018.157</v>
+      </c>
+      <c r="D212" t="n">
+        <v>663.9219999999999</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2080.195</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1195.625</v>
+      </c>
+      <c r="D213" t="n">
+        <v>884.5700000000002</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D211"/>
+  <dimension ref="A1:D213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7166,13 +7198,13 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1162.754</v>
+        <v>1166.092</v>
       </c>
       <c r="C209" t="n">
-        <v>827.77</v>
+        <v>820.8019999999999</v>
       </c>
       <c r="D209" t="n">
-        <v>1990.524</v>
+        <v>1986.894</v>
       </c>
     </row>
     <row r="210">
@@ -7182,13 +7214,13 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>1213.874</v>
+        <v>1218.445</v>
       </c>
       <c r="C210" t="n">
-        <v>261.1120000000001</v>
+        <v>252.9560000000001</v>
       </c>
       <c r="D210" t="n">
-        <v>1474.986</v>
+        <v>1471.401</v>
       </c>
     </row>
     <row r="211">
@@ -7198,13 +7230,45 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>1175.867</v>
+        <v>1180.552</v>
       </c>
       <c r="C211" t="n">
-        <v>918.486</v>
+        <v>901.035</v>
       </c>
       <c r="D211" t="n">
-        <v>2094.353</v>
+        <v>2081.587</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1018.157</v>
+      </c>
+      <c r="C212" t="n">
+        <v>663.9219999999999</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1682.079</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1195.625</v>
+      </c>
+      <c r="C213" t="n">
+        <v>884.5700000000002</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2080.195</v>
       </c>
     </row>
   </sheetData>
